--- a/data/trans_orig/P36B08_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P36B08_R-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>632592</t>
+          <t>629252</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>693891</t>
+          <t>689821</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>61,36%</t>
+          <t>61,04%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>67,31%</t>
+          <t>66,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>927218</t>
+          <t>927572</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>991006</t>
+          <t>991585</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>70,5%</t>
+          <t>70,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>75,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1570150</t>
+          <t>1578313</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1659357</t>
+          <t>1660859</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>66,93%</t>
+          <t>67,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>70,73%</t>
+          <t>70,8%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>336998</t>
+          <t>341068</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>398297</t>
+          <t>401637</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>38,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>324107</t>
+          <t>323528</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>387895</t>
+          <t>387541</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>686644</t>
+          <t>685142</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>775851</t>
+          <t>767688</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>32,72%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1001336</t>
+          <t>1003160</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1085929</t>
+          <t>1088077</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>59,13%</t>
+          <t>59,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>64,13%</t>
+          <t>64,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1067980</t>
+          <t>1068601</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1141910</t>
+          <t>1142314</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,47 +1126,47 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
+          <t>67,35%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>72,0%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>2082</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>2149688</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>2096917</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>2207928</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>65,54%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>63,93%</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
           <t>67,31%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>71,97%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2082</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>2149688</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>2090159</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>2202396</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>65,54%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>63,72%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>67,15%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>607484</t>
+          <t>605336</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>692077</t>
+          <t>690253</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>35,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>40,87%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>444703</t>
+          <t>444299</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>518633</t>
+          <t>518012</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,47 +1239,47 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
+          <t>32,65%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>1120</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>1130338</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>1072098</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>1183109</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>34,46%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
           <t>32,69%</t>
         </is>
       </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1120</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1130338</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>1077630</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>1189867</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>34,46%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>32,85%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>36,07%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>339807</t>
+          <t>340996</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>386661</t>
+          <t>387595</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>61,63%</t>
+          <t>61,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>70,12%</t>
+          <t>70,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>318117</t>
+          <t>316132</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>355086</t>
+          <t>355132</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>66,77%</t>
+          <t>66,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>74,53%</t>
+          <t>74,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>675218</t>
+          <t>674115</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>732074</t>
+          <t>733612</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>65,69%</t>
+          <t>65,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>71,23%</t>
+          <t>71,38%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>164747</t>
+          <t>163813</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>211601</t>
+          <t>210412</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>38,37%</t>
+          <t>38,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>121326</t>
+          <t>121280</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>158295</t>
+          <t>160280</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>295746</t>
+          <t>294208</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>352602</t>
+          <t>353705</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>34,41%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2013745</t>
+          <t>2020508</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2128375</t>
+          <t>2125928</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>61,48%</t>
+          <t>61,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>64,97%</t>
+          <t>64,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2341215</t>
+          <t>2344836</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2449848</t>
+          <t>2451375</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>69,3%</t>
+          <t>69,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>72,52%</t>
+          <t>72,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4397999</t>
+          <t>4385114</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4555090</t>
+          <t>4542259</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>66,1%</t>
+          <t>65,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>68,46%</t>
+          <t>68,27%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1147334</t>
+          <t>1149781</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1261964</t>
+          <t>1255201</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>38,52%</t>
+          <t>38,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>928289</t>
+          <t>926762</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1036922</t>
+          <t>1033301</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2098757</t>
+          <t>2111588</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2255848</t>
+          <t>2268733</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>34,1%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>681248</t>
+          <t>676509</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>738293</t>
+          <t>735193</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>70,19%</t>
+          <t>69,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>76,07%</t>
+          <t>75,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1046749</t>
+          <t>1048308</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1106793</t>
+          <t>1107819</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>78,24%</t>
+          <t>78,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>82,73%</t>
+          <t>82,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1748309</t>
+          <t>1740562</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1828635</t>
+          <t>1828567</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>75,74%</t>
+          <t>75,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>232217</t>
+          <t>235317</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>289262</t>
+          <t>294001</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>231004</t>
+          <t>229978</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>291048</t>
+          <t>289489</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>479671</t>
+          <t>479739</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>559997</t>
+          <t>567744</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,6%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1316583</t>
+          <t>1315939</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1404547</t>
+          <t>1398879</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>67,11%</t>
+          <t>67,07%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>71,59%</t>
+          <t>71,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1318318</t>
+          <t>1318870</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1387984</t>
+          <t>1387499</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>75,34%</t>
+          <t>75,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>79,32%</t>
+          <t>79,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2658925</t>
+          <t>2653359</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2772696</t>
+          <t>2767576</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>71,63%</t>
+          <t>71,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>74,7%</t>
+          <t>74,56%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>557366</t>
+          <t>563034</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>645330</t>
+          <t>645974</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>361922</t>
+          <t>362407</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>431588</t>
+          <t>431036</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>939123</t>
+          <t>944243</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1052894</t>
+          <t>1058460</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>28,52%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>342365</t>
+          <t>342487</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>380764</t>
+          <t>380212</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>71,3%</t>
+          <t>71,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>79,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>370572</t>
+          <t>371738</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>402788</t>
+          <t>403255</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>81,14%</t>
+          <t>81,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>88,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>722630</t>
+          <t>722561</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>774524</t>
+          <t>772652</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>82,47%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>99388</t>
+          <t>99940</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>137787</t>
+          <t>137665</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>53908</t>
+          <t>53441</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>86124</t>
+          <t>84958</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>162324</t>
+          <t>164196</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>214218</t>
+          <t>214287</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2374169</t>
+          <t>2368457</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2486711</t>
+          <t>2478583</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>69,57%</t>
+          <t>69,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>72,87%</t>
+          <t>72,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2769034</t>
+          <t>2772587</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2865902</t>
+          <t>2868163</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>78,12%</t>
+          <t>78,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>80,86%</t>
+          <t>80,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5172303</t>
+          <t>5174131</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5318060</t>
+          <t>5329196</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>74,35%</t>
+          <t>74,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>76,44%</t>
+          <t>76,6%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>925863</t>
+          <t>933991</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1038405</t>
+          <t>1044117</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>678496</t>
+          <t>676235</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>775364</t>
+          <t>771811</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1638913</t>
+          <t>1627777</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1784670</t>
+          <t>1782842</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,63%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>554045</t>
+          <t>552266</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>599698</t>
+          <t>595816</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>73,64%</t>
+          <t>73,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>79,71%</t>
+          <t>79,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>754561</t>
+          <t>758893</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>810544</t>
+          <t>812431</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>76,2%</t>
+          <t>76,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>81,86%</t>
+          <t>82,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1325055</t>
+          <t>1322716</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1397818</t>
+          <t>1392991</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>76,04%</t>
+          <t>75,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>80,22%</t>
+          <t>79,94%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>152690</t>
+          <t>156572</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>198343</t>
+          <t>200122</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>179647</t>
+          <t>177760</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>235630</t>
+          <t>231298</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>344761</t>
+          <t>349588</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>417524</t>
+          <t>419863</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>24,09%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1386213</t>
+          <t>1382707</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1471325</t>
+          <t>1469026</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>67,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>71,31%</t>
+          <t>71,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1443901</t>
+          <t>1446583</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1522177</t>
+          <t>1522904</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>73,0%</t>
+          <t>73,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>76,96%</t>
+          <t>76,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2850275</t>
+          <t>2853009</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2970913</t>
+          <t>2972825</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>70,53%</t>
+          <t>70,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>73,52%</t>
+          <t>73,56%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>591850</t>
+          <t>594149</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>676962</t>
+          <t>680468</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>455798</t>
+          <t>455071</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>534074</t>
+          <t>531392</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1070237</t>
+          <t>1068325</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1190875</t>
+          <t>1188141</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>29,4%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>406087</t>
+          <t>400867</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>446468</t>
+          <t>443869</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>74,53%</t>
+          <t>73,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>81,94%</t>
+          <t>81,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>429362</t>
+          <t>428757</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>465530</t>
+          <t>464831</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>78,47%</t>
+          <t>78,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>85,08%</t>
+          <t>84,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>848537</t>
+          <t>846088</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>899600</t>
+          <t>900114</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>77,7%</t>
+          <t>77,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>82,38%</t>
+          <t>82,42%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>98408</t>
+          <t>101007</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>138789</t>
+          <t>144009</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>81646</t>
+          <t>82345</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>117814</t>
+          <t>118419</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>192452</t>
+          <t>191938</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>243515</t>
+          <t>245964</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,52%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2380244</t>
+          <t>2376037</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2481746</t>
+          <t>2482404</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>70,83%</t>
+          <t>70,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>73,85%</t>
+          <t>73,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2669424</t>
+          <t>2671238</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2772842</t>
+          <t>2769068</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>75,94%</t>
+          <t>75,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>78,88%</t>
+          <t>78,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5069478</t>
+          <t>5069034</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5222110</t>
+          <t>5220895</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>73,73%</t>
+          <t>73,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>75,95%</t>
+          <t>75,93%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>878693</t>
+          <t>878035</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>980195</t>
+          <t>984402</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>742501</t>
+          <t>746275</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>845919</t>
+          <t>844105</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1653672</t>
+          <t>1654887</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1806304</t>
+          <t>1806748</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>26,28%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>477259</t>
+          <t>539690</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>463841</t>
+          <t>527395</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>486565</t>
+          <t>550379</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>712521</t>
+          <t>776408</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>702458</t>
+          <t>766077</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>721257</t>
+          <t>785593</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1189780</t>
+          <t>1316098</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1172509</t>
+          <t>1300245</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1202934</t>
+          <t>1332032</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>95,3%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>36938</t>
+          <t>38071</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27632</t>
+          <t>27382</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>50356</t>
+          <t>50366</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>40954</t>
+          <t>43570</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>32218</t>
+          <t>34385</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>51017</t>
+          <t>53901</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>77892</t>
+          <t>81641</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>64738</t>
+          <t>65707</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>95163</t>
+          <t>97494</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>6,98%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>514197</t>
+          <t>577761</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>514197</t>
+          <t>577761</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>514197</t>
+          <t>577761</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>753475</t>
+          <t>819978</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>753475</t>
+          <t>819978</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>753475</t>
+          <t>819978</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1267672</t>
+          <t>1397739</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1267672</t>
+          <t>1397739</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1267672</t>
+          <t>1397739</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2152873</t>
+          <t>2090869</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2114643</t>
+          <t>2060569</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2190775</t>
+          <t>2115548</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2150753</t>
+          <t>2080003</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2123352</t>
+          <t>2058745</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2175007</t>
+          <t>2096954</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>4303625</t>
+          <t>4170873</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4255908</t>
+          <t>4131480</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4350261</t>
+          <t>4201549</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>95,55%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>134909</t>
+          <t>136891</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>97007</t>
+          <t>112212</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>173139</t>
+          <t>167191</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>85205</t>
+          <t>89324</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>60951</t>
+          <t>72373</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>112606</t>
+          <t>110582</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>220114</t>
+          <t>226214</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>173478</t>
+          <t>195538</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>267831</t>
+          <t>265607</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,04%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2287782</t>
+          <t>2227760</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2287782</t>
+          <t>2227760</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2287782</t>
+          <t>2227760</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2235958</t>
+          <t>2169327</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2235958</t>
+          <t>2169327</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2235958</t>
+          <t>2169327</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4523739</t>
+          <t>4397087</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4523739</t>
+          <t>4397087</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4523739</t>
+          <t>4397087</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>626623</t>
+          <t>688398</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>616032</t>
+          <t>675666</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>634935</t>
+          <t>696954</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>637879</t>
+          <t>710243</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>625116</t>
+          <t>697393</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>646109</t>
+          <t>718482</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1264502</t>
+          <t>1398642</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1247349</t>
+          <t>1381989</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1276375</t>
+          <t>1411211</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,56%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>23189</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11688</t>
+          <t>14633</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>30591</t>
+          <t>35921</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>22584</t>
+          <t>24634</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14354</t>
+          <t>16395</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>35347</t>
+          <t>37484</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>42584</t>
+          <t>47822</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>30711</t>
+          <t>35253</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>59737</t>
+          <t>64475</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3256754</t>
+          <t>3318956</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3219165</t>
+          <t>3288790</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3303552</t>
+          <t>3352335</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3501153</t>
+          <t>3566656</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3470106</t>
+          <t>3542537</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3529424</t>
+          <t>3590680</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>6757907</t>
+          <t>6885612</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6711121</t>
+          <t>6843790</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6813273</t>
+          <t>6926527</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,65%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>191848</t>
+          <t>198151</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>145050</t>
+          <t>164772</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>229437</t>
+          <t>228317</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>148743</t>
+          <t>157527</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>120472</t>
+          <t>133503</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>179790</t>
+          <t>181646</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>340591</t>
+          <t>355678</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>285225</t>
+          <t>314763</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>387377</t>
+          <t>397500</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,49%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3448602</t>
+          <t>3517107</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3448602</t>
+          <t>3517107</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3448602</t>
+          <t>3517107</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3649896</t>
+          <t>3724183</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3649896</t>
+          <t>3724183</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3649896</t>
+          <t>3724183</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7098498</t>
+          <t>7241290</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7098498</t>
+          <t>7241290</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7098498</t>
+          <t>7241290</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">

--- a/data/trans_orig/P36B08_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P36B08_R-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si consumen 3 veces o más a la semana verduras, ensaladas y hortalizas en 2007 (tasa de respuesta: 99,97%)</t>
+          <t>Población según si consumen 3 veces o más a la semana verduras, ensaladas y hortalizas [2023 pregunta frecuencias diarias, ediciones anteriores frecuencias semanales] en 2007 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si consumen 3 veces o más a la semana verduras, ensaladas y hortalizas en 2012 (tasa de respuesta: 99,78%)</t>
+          <t>Población según si consumen 3 veces o más a la semana verduras, ensaladas y hortalizas [2023 pregunta frecuencias diarias, ediciones anteriores frecuencias semanales] en 2012 (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si consumen 3 veces o más a la semana verduras, ensaladas y hortalizas en 2016 (tasa de respuesta: 99,53%)</t>
+          <t>Población según si consumen 3 veces o más a la semana verduras, ensaladas y hortalizas [2023 pregunta frecuencias diarias, ediciones anteriores frecuencias semanales] en 2016 (tasa de respuesta: 99,53%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si consumen 3 veces o más a la semana verduras, ensaladas y hortalizas en 2023 (tasa de respuesta: 99,86%)</t>
+          <t>Población según si consumen 3 veces o más a la semana verduras, ensaladas y hortalizas [2023 pregunta frecuencias diarias, ediciones anteriores frecuencias semanales] en 2023 (tasa de respuesta: 99,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
